--- a/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,16 +38,16 @@
     <t>P7-127</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KCN-0704</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KCN-0004</t>
   </si>
   <si>
     <t>Đường kính</t>
   </si>
   <si>
-    <t>800</t>
+    <t>D800</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">06:20
@@ -112,9 +112,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>Đất thổ nhưỡng</t>
-  </si>
-  <si>
     <t xml:space="preserve">06:30
 10/03/2026</t>
   </si>
@@ -136,7 +133,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">07:35
@@ -178,7 +175,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">09:26
@@ -206,7 +203,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:12
@@ -218,9 +215,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:20
@@ -265,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -336,16 +330,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -358,7 +342,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,17 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -622,34 +596,16 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1254,334 +1210,334 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="F12" s="5">
         <v>-0.847</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="5">
         <v>-1.447</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="5">
         <v>0.07</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="5">
         <v>0.6</v>
       </c>
       <c r="J12" s="8">
         <v>9</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="F13" s="9">
         <v>-1.447</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="9">
         <v>-6.547</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="9">
         <v>0.92</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="9">
         <v>5.1</v>
       </c>
       <c r="J13" s="8">
         <v>5.56</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="15">
+      <c r="F14" s="12">
         <v>-6.547</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="12">
         <v>-9.847</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="12">
         <v>0.5</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="12">
         <v>3.3</v>
       </c>
       <c r="J14" s="8">
         <v>6.6</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="E15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="18">
+      <c r="F15" s="15">
         <v>-9.847</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="15">
         <v>-18.047</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="15">
         <v>0.92</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="15">
         <v>8.2</v>
       </c>
       <c r="J15" s="8">
         <v>8.95</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="22" t="s">
+      <c r="D16" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="E16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="21">
+      <c r="F16" s="18">
         <v>-18.047</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="18">
         <v>-23.247</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="18">
         <v>0.32</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="18">
         <v>5.2</v>
       </c>
       <c r="J16" s="8">
         <v>16.42</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="E17" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="24">
+      <c r="F17" s="21">
         <v>-23.247</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="21">
         <v>-27.247</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="21">
         <v>0.32</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="21">
         <v>4</v>
       </c>
       <c r="J17" s="8">
         <v>12.63</v>
       </c>
-      <c r="K17" s="25" t="s">
+      <c r="K17" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="28" t="s">
+      <c r="D18" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="E18" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="27">
+      <c r="F18" s="24">
         <v>-27.247</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="24">
         <v>-40.197</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="24">
         <v>0.32</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="24">
         <v>12.95</v>
       </c>
       <c r="J18" s="8">
         <v>40.89</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="D19" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="27">
+        <v>-40.197</v>
+      </c>
+      <c r="G19" s="27">
+        <v>-44.277</v>
+      </c>
+      <c r="H19" s="27">
+        <v>1.1</v>
+      </c>
+      <c r="I19" s="27">
+        <v>4.08</v>
+      </c>
+      <c r="J19" s="30">
+        <v>3.71</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="30">
-        <v>-40.197</v>
-      </c>
-      <c r="G19" s="30">
+      <c r="C20" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="27">
         <v>-44.277</v>
       </c>
-      <c r="H19" s="30">
-        <v>1.1</v>
-      </c>
-      <c r="I19" s="30">
-        <v>4.08</v>
-      </c>
-      <c r="J19" s="33">
-        <v>3.71</v>
-      </c>
-      <c r="K19" s="31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-44.277</v>
-      </c>
-      <c r="G20" s="34">
+      <c r="G20" s="27">
         <v>-45.04</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="27">
         <v>0.08</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="27">
         <v>0.76</v>
       </c>
       <c r="J20" s="8">
         <v>9.16</v>
       </c>
-      <c r="K20" s="35" t="s">
+      <c r="K20" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1663,7 +1619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1676,31 +1632,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,22 +1670,22 @@
         <v>27</v>
       </c>
       <c r="D2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5">
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-0.85</v>
+        <v>-1.45</v>
       </c>
       <c r="G2" s="5">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>0.85</v>
+        <v>1.45</v>
       </c>
       <c r="I2" s="8">
-        <v>8.47</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1740,25 +1696,25 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-0.85</v>
+        <v>-1.45</v>
       </c>
       <c r="F3" s="9">
-        <v>-1.45</v>
+        <v>-6.55</v>
       </c>
       <c r="G3" s="9">
-        <v>0.07</v>
+        <v>0.92</v>
       </c>
       <c r="H3" s="9">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="I3" s="8">
-        <v>9</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,25 +1725,25 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-1.45</v>
+        <v>-6.55</v>
       </c>
       <c r="F4" s="12">
-        <v>-6.55</v>
+        <v>-9.85</v>
       </c>
       <c r="G4" s="12">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="12">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="8">
-        <v>5.56</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,25 +1754,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-6.55</v>
+        <v>-9.85</v>
       </c>
       <c r="F5" s="15">
-        <v>-9.85</v>
+        <v>-18.05</v>
       </c>
       <c r="G5" s="15">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H5" s="15">
-        <v>3.3</v>
+        <v>8.2</v>
       </c>
       <c r="I5" s="8">
-        <v>6.6</v>
+        <v>8.95</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1827,25 +1783,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-9.85</v>
+        <v>-18.05</v>
       </c>
       <c r="F6" s="18">
-        <v>-18.05</v>
+        <v>-23.25</v>
       </c>
       <c r="G6" s="18">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="H6" s="18">
-        <v>8.2</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>8.95</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1856,25 +1812,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-18.05</v>
+        <v>-23.25</v>
       </c>
       <c r="F7" s="21">
-        <v>-23.25</v>
+        <v>-27.25</v>
       </c>
       <c r="G7" s="21">
         <v>0.32</v>
       </c>
       <c r="H7" s="21">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="8">
-        <v>16.42</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1885,25 +1841,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-23.25</v>
+        <v>-27.25</v>
       </c>
       <c r="F8" s="24">
-        <v>-27.25</v>
+        <v>-40.2</v>
       </c>
       <c r="G8" s="24">
         <v>0.32</v>
       </c>
       <c r="H8" s="24">
-        <v>4</v>
+        <v>12.95</v>
       </c>
       <c r="I8" s="8">
-        <v>12.63</v>
+        <v>40.89</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1914,111 +1870,53 @@
         <v>11</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="27">
-        <v>-27.25</v>
+        <v>-40.2</v>
       </c>
       <c r="F9" s="27">
-        <v>-40.2</v>
+        <v>-45.04</v>
       </c>
       <c r="G9" s="27">
-        <v>0.32</v>
+        <v>1.18</v>
       </c>
       <c r="H9" s="27">
-        <v>12.95</v>
-      </c>
-      <c r="I9" s="8">
-        <v>40.89</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
-        <v>9</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="30">
-        <v>1</v>
-      </c>
-      <c r="E10" s="30">
-        <v>-40.2</v>
-      </c>
-      <c r="F10" s="30">
-        <v>-44.28</v>
-      </c>
-      <c r="G10" s="30">
-        <v>1.1</v>
-      </c>
-      <c r="H10" s="30">
-        <v>4.08</v>
+        <v>4.84</v>
+      </c>
+      <c r="I9" s="30">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="33">
+        <v>10</v>
+      </c>
+      <c r="E10" s="33">
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
+        <v>-45.04</v>
+      </c>
+      <c r="G10" s="33">
+        <v>4.63</v>
+      </c>
+      <c r="H10" s="33">
+        <v>45.04</v>
       </c>
       <c r="I10" s="33">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-44.28</v>
-      </c>
-      <c r="F11" s="34">
-        <v>-45.04</v>
-      </c>
-      <c r="G11" s="34">
-        <v>0.08</v>
-      </c>
-      <c r="H11" s="34">
-        <v>0.76</v>
-      </c>
-      <c r="I11" s="8">
-        <v>9.16</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39">
-        <v>-45.04</v>
-      </c>
-      <c r="G12" s="39">
-        <v>4.63</v>
-      </c>
-      <c r="H12" s="39">
-        <v>45.04</v>
-      </c>
-      <c r="I12" s="39">
         <v>9.72</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCN-0004</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,9 +106,6 @@
 10/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -119,7 +116,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">06:35
@@ -147,9 +144,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">08:10
 10/03/2026</t>
   </si>
@@ -175,7 +169,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">09:26
@@ -187,9 +181,6 @@
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">09:46
@@ -259,7 +250,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -325,11 +316,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF164E63"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -342,7 +328,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,11 +388,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -507,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -587,25 +568,16 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,12 +1178,12 @@
         <v>8.47</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>11</v>
@@ -1223,7 +1195,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="5">
         <v>-0.847</v>
@@ -1241,24 +1213,24 @@
         <v>9</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="9">
         <v>-1.447</v>
@@ -1276,24 +1248,24 @@
         <v>5.56</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="E14" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="12">
         <v>-6.547</v>
@@ -1311,24 +1283,24 @@
         <v>6.6</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="15">
         <v>-9.847</v>
@@ -1346,24 +1318,24 @@
         <v>8.95</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>48</v>
       </c>
       <c r="F16" s="18">
         <v>-18.047</v>
@@ -1381,24 +1353,24 @@
         <v>16.42</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>52</v>
       </c>
       <c r="F17" s="21">
         <v>-23.247</v>
@@ -1416,128 +1388,128 @@
         <v>12.63</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="24">
+      <c r="F18" s="21">
         <v>-27.247</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="21">
         <v>-40.197</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="21">
         <v>0.32</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="21">
         <v>12.95</v>
       </c>
       <c r="J18" s="8">
         <v>40.89</v>
       </c>
-      <c r="K18" s="25" t="s">
-        <v>30</v>
+      <c r="K18" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="F19" s="24">
+        <v>-40.197</v>
+      </c>
+      <c r="G19" s="24">
+        <v>-44.277</v>
+      </c>
+      <c r="H19" s="24">
+        <v>1.1</v>
+      </c>
+      <c r="I19" s="24">
+        <v>4.08</v>
+      </c>
+      <c r="J19" s="27">
+        <v>3.71</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="29" t="s">
+      <c r="C20" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E20" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="27">
-        <v>-40.197</v>
-      </c>
-      <c r="G19" s="27">
+      <c r="F20" s="24">
         <v>-44.277</v>
       </c>
-      <c r="H19" s="27">
-        <v>1.1</v>
-      </c>
-      <c r="I19" s="27">
-        <v>4.08</v>
-      </c>
-      <c r="J19" s="30">
-        <v>3.71</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="F20" s="27">
-        <v>-44.277</v>
-      </c>
-      <c r="G20" s="27">
+      <c r="G20" s="24">
         <v>-45.04</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="24">
         <v>0.08</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="24">
         <v>0.76</v>
       </c>
       <c r="J20" s="8">
         <v>9.16</v>
       </c>
-      <c r="K20" s="28" t="s">
-        <v>30</v>
+      <c r="K20" s="25" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
+      <c r="A23" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1619,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1632,31 +1604,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1696,7 +1668,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1725,7 +1697,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1754,7 +1726,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1783,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1812,25 +1784,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="21">
         <v>-23.25</v>
       </c>
       <c r="F7" s="21">
-        <v>-27.25</v>
+        <v>-40.2</v>
       </c>
       <c r="G7" s="21">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="21">
-        <v>4</v>
+        <v>16.95</v>
       </c>
       <c r="I7" s="8">
-        <v>12.63</v>
+        <v>26.76</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1841,82 +1813,53 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="24">
-        <v>-27.25</v>
+        <v>-40.2</v>
       </c>
       <c r="F8" s="24">
-        <v>-40.2</v>
+        <v>-45.04</v>
       </c>
       <c r="G8" s="24">
-        <v>0.32</v>
+        <v>1.18</v>
       </c>
       <c r="H8" s="24">
-        <v>12.95</v>
-      </c>
-      <c r="I8" s="8">
-        <v>40.89</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
-        <v>8</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="27">
-        <v>2</v>
-      </c>
-      <c r="E9" s="27">
-        <v>-40.2</v>
-      </c>
-      <c r="F9" s="27">
+        <v>4.84</v>
+      </c>
+      <c r="I8" s="27">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="30">
+        <v>10</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
         <v>-45.04</v>
       </c>
-      <c r="G9" s="27">
-        <v>1.18</v>
-      </c>
-      <c r="H9" s="27">
-        <v>4.84</v>
+      <c r="G9" s="30">
+        <v>4.63</v>
+      </c>
+      <c r="H9" s="30">
+        <v>45.04</v>
       </c>
       <c r="I9" s="30">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="33">
-        <v>10</v>
-      </c>
-      <c r="E10" s="33">
-        <v>0</v>
-      </c>
-      <c r="F10" s="33">
-        <v>-45.04</v>
-      </c>
-      <c r="G10" s="33">
-        <v>4.63</v>
-      </c>
-      <c r="H10" s="33">
-        <v>45.04</v>
-      </c>
-      <c r="I10" s="33">
         <v>9.72</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/f7ae0a3d-0a6e-4220-aba8-0160a7a705dc_Phường_Hạc_Thành__tỉnh_Thanh_Hoa_P7-127_800_10-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">06:26
 10/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1178,12 +1181,12 @@
         <v>8.47</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>11</v>
@@ -1195,7 +1198,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="5">
         <v>-0.847</v>
@@ -1213,24 +1216,24 @@
         <v>9</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="9">
         <v>-1.447</v>
@@ -1248,24 +1251,24 @@
         <v>5.56</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="12">
         <v>-6.547</v>
@@ -1283,24 +1286,24 @@
         <v>6.6</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="15">
         <v>-9.847</v>
@@ -1318,24 +1321,24 @@
         <v>8.95</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" s="18">
         <v>-18.047</v>
@@ -1353,24 +1356,24 @@
         <v>16.42</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="21">
         <v>-23.247</v>
@@ -1388,24 +1391,24 @@
         <v>12.63</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="21">
         <v>-27.247</v>
@@ -1423,24 +1426,24 @@
         <v>40.89</v>
       </c>
       <c r="K18" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F19" s="24">
         <v>-40.197</v>
@@ -1458,24 +1461,24 @@
         <v>3.71</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="24">
         <v>-44.277</v>
@@ -1493,12 +1496,12 @@
         <v>9.16</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -1604,31 +1607,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1668,7 +1671,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1697,7 +1700,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1726,7 +1729,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1755,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1784,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="21">
         <v>2</v>
@@ -1813,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="24">
         <v>2</v>
@@ -1836,13 +1839,13 @@
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D9" s="30">
         <v>10</v>
